--- a/data/trans_camb/IP11-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.784530531468504</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.645873556866009</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.041421846154964</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.715207768637174</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-2.895637856679011</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-4.312541430048354</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-7.132950029622269</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.22809710664933</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.728093936526519</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.192554877916552</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-5.69363703150711</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-7.351439310282609</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.6028920087796178</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-2.337716403157421</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4337470264953965</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.334204401788042</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.3477158305497008</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.9680862464322799</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.3103270574768582</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.740661437164356</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3806073890203771</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.2146432765562504</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3409058721958777</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5077191176377357</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5818158594339494</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.9656775921391787</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.655547236080087</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6763032772320721</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5571042240723467</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7667356595444795</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1367874126958683</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-0.1538965781459408</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1006897572575566</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.733833659043117</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.04778869573210148</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.09528060487413895</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-7.497034892378665</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-9.874133785171638</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.853237938130044</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-6.07629140675888</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-6.169958219537446</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-7.928831090087954</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-11.87294329201662</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-14.48774214527807</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.053961534818495</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.087436485407524</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-9.188647908977327</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-10.71527387169564</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>-3.545419289710923</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-6.117618873489557</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-1.572612693730834</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-3.27064359750906</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-3.637456329453276</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-5.46488870575309</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.5923051399158449</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.780108439820565</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.6746755378109696</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.8446989875651493</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.621505318161108</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.7986781294055878</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.7747298608505446</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.9181339265510948</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.8746090774216329</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.9537634721424423</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7800241039375866</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9025063298992254</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>-0.2923965963538847</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.5510163037680115</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.2410487160048759</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.5494918508547064</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.4185624361062411</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.6399594816920601</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-3.219981895682972</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.980953332174254</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-5.935892531126344</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.080373229101455</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-4.619704820592451</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-4.546459379238163</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-7.722046208387451</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-9.81954735507329</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.835864809934291</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.20775051242062</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-8.004635048416416</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-7.451549320465725</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>1.352767854929319</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.9412575043524862</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-2.451807864307218</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.2956291059871818</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-1.628948765226452</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-1.860005340908448</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.4074848275177372</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.6303336401226642</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.8233583374535338</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.5659821670432754</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.6109695745231307</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.6012826490857065</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.7482849548399367</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8554277741767388</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.954420126244852</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.842440574936738</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8075372584735362</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.7915343834263467</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.3520558865514877</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.09629987598976367</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.3754719551214742</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.007924931529964367</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.1768452697712411</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.2753460506876262</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-3.022439796460692</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-2.975715550072843</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.4776754682007827</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.459437974736908</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.414526956276474</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-2.395846533445808</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-9.525947162195026</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-9.278364012862946</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-4.702894175214833</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-6.004206984822519</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-6.170096011096374</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-6.477900277082145</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.52648405002669</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.979682778578749</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>5.207513118879544</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.001695130773165</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.325211703753585</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.896089636152814</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.3773206467856385</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.3714876032662012</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1336970582191987</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.4084835350884993</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2360159827595049</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3997506527699177</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.7810628388735587</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.7660624308371429</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.8376743954806082</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.9197529542318494</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6926446630532014</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.7249496786151387</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.7116873195359469</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.5418209854604124</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>3.876652898095971</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2.525809996236029</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.5970412456576727</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.2632996939767662</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-4.287663393350844</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-6.481786878713073</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-3.774997123489078</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-4.341546934293595</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-4.029086974777404</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-5.426461309047534</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-6.680693561749497</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-8.567205539943377</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-5.725516942655966</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-6.282933919125106</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-5.483876093362906</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-6.922197364981657</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-2.084217188450841</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-4.37770543007572</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-2.015839147099585</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-2.124702489280895</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-2.38738789164507</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-4.038726904001599</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.4407044131187027</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.6662258251833837</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.5349935810214587</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.615285168589397</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.4782847294570657</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.6441641978330396</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5953263555571175</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7815348296765069</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.6883766904438845</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.7728997576300491</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.5938695555429823</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.7418176260287259</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.2397152747255473</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.4922786621660668</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.3105382142870174</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.3709583773514171</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.3218930718245165</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.5161598073779896</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
